--- a/out/C03_b2b_saas_decision_journey/agent3/agent3_test_cases_with_paths.xlsx
+++ b/out/C03_b2b_saas_decision_journey/agent3/agent3_test_cases_with_paths.xlsx
@@ -114,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -145,9 +145,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1572,7 +1569,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved</t>
+          <t>Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1592,7 +1589,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Q1 = None of these; Q10 = No; Q12 = Not resolved; Q15 = No; Q16 = Price; Q3 = None/currently not using; Q5 = None of these; S1 = Yes; S2 = A decision-maker or major influencer for business software; S3 = No; S4 = No</t>
+          <t>Q1 = Open-source alternative; Q10 = No; Q12 = Not resolved; Q15 = No; Q16 = Price; Q3 = None/currently not using; Q5 = None of these; S1 = Yes; S2 = A decision-maker or major influencer for business software; S3 = No; S4 = No</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -1607,12 +1604,12 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Q6, Q7, Q8, Q9, Q11, Q12, Q13, Q15, Q16, Q17</t>
+          <t>Q2, Q3, Q6, Q7, Q8, Q9, Q11, Q12, Q13, Q15, Q16, Q17</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
@@ -1622,7 +1619,7 @@
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>R15, R5</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -3914,7 +3911,7 @@
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as DT1.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as DT1.</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
@@ -3955,7 +3952,7 @@
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U17" s="6" t="inlineStr">
@@ -4070,7 +4067,7 @@
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q1.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q1.</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
@@ -4111,7 +4108,7 @@
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U18" s="6" t="inlineStr">
@@ -4228,7 +4225,7 @@
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q1.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q1.</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
@@ -4269,7 +4266,7 @@
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U19" s="6" t="inlineStr">
@@ -4386,7 +4383,7 @@
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q1.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q1.</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
@@ -4427,7 +4424,7 @@
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U20" s="6" t="inlineStr">
@@ -4544,7 +4541,7 @@
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q1.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q1.</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
@@ -4585,7 +4582,7 @@
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U21" s="6" t="inlineStr">
@@ -4701,7 +4698,7 @@
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q1.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q1.</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
@@ -4742,7 +4739,7 @@
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U22" s="6" t="inlineStr">
@@ -4859,7 +4856,7 @@
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q1.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q1.</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
@@ -4900,7 +4897,7 @@
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U23" s="6" t="inlineStr">
@@ -5017,7 +5014,7 @@
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q1.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q1.</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
@@ -5058,7 +5055,7 @@
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U24" s="6" t="inlineStr">
@@ -5216,7 +5213,7 @@
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U25" s="6" t="inlineStr">
@@ -5658,7 +5655,7 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = A decision-maker or major influencer for business software; S3 = No; S4 = No; Q1 = None of these
+          <t>S1 = Yes; S2 = A decision-maker or major influencer for business software; S3 = No; S4 = No; Q1 = Open-source alternative
 then: After submitting Q1, look for Q2 on the next page. Do not answer it.</t>
         </is>
       </c>
@@ -5747,7 +5744,7 @@
       </c>
       <c r="AE28" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6601,7 @@
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = A decision-maker or major influencer for business software; S3 = No; S4 = No; Q1 = None of these
+          <t>S1 = Yes; S2 = A decision-maker or major influencer for business software; S3 = No; S4 = No; Q1 = Open-source alternative
 then: After submitting Q1, look for Q3 on the next page. Do not answer it.</t>
         </is>
       </c>
@@ -6692,7 +6689,7 @@
       </c>
       <c r="AE34" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6906,7 @@
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q4.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q4.</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
@@ -6950,7 +6947,7 @@
       </c>
       <c r="T36" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U36" s="6" t="inlineStr">
@@ -7066,7 +7063,7 @@
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q4.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q4.</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
@@ -7107,7 +7104,7 @@
       </c>
       <c r="T37" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U37" s="6" t="inlineStr">
@@ -7223,7 +7220,7 @@
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q5.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q5.</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
@@ -7264,7 +7261,7 @@
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U38" s="6" t="inlineStr">
@@ -7381,7 +7378,7 @@
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q5.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q5.</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
@@ -7422,7 +7419,7 @@
       </c>
       <c r="T39" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U39" s="6" t="inlineStr">
@@ -7538,7 +7535,7 @@
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q5.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q5.</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr">
@@ -7579,7 +7576,7 @@
       </c>
       <c r="T40" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U40" s="6" t="inlineStr">
@@ -7696,7 +7693,7 @@
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q5.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q5.</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
@@ -7737,7 +7734,7 @@
       </c>
       <c r="T41" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U41" s="6" t="inlineStr">
@@ -7854,7 +7851,7 @@
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q5.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q5.</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr">
@@ -7895,7 +7892,7 @@
       </c>
       <c r="T42" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U42" s="6" t="inlineStr">
@@ -8013,7 +8010,7 @@
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q5.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q5.</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr">
@@ -8054,7 +8051,7 @@
       </c>
       <c r="T43" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U43" s="6" t="inlineStr">
@@ -8171,7 +8168,7 @@
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q5.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q5.</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr">
@@ -8212,7 +8209,7 @@
       </c>
       <c r="T44" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U44" s="6" t="inlineStr">
@@ -8370,7 +8367,7 @@
       </c>
       <c r="T45" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U45" s="6" t="inlineStr">
@@ -12280,7 +12277,7 @@
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as DT2.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as DT2.</t>
         </is>
       </c>
       <c r="M70" s="6" t="inlineStr">
@@ -12321,7 +12318,7 @@
       </c>
       <c r="T70" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U70" s="6" t="inlineStr">
@@ -12436,7 +12433,7 @@
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q10.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q10.</t>
         </is>
       </c>
       <c r="M71" s="6" t="inlineStr">
@@ -12477,7 +12474,7 @@
       </c>
       <c r="T71" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U71" s="6" t="inlineStr">
@@ -12593,7 +12590,7 @@
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q10.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q10.</t>
         </is>
       </c>
       <c r="M72" s="6" t="inlineStr">
@@ -12634,7 +12631,7 @@
       </c>
       <c r="T72" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U72" s="6" t="inlineStr">
@@ -14956,7 +14953,7 @@
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q14.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q14.</t>
         </is>
       </c>
       <c r="M87" s="6" t="inlineStr">
@@ -14997,7 +14994,7 @@
       </c>
       <c r="T87" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U87" s="6" t="inlineStr">
@@ -15114,7 +15111,7 @@
       </c>
       <c r="L88" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q14.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q14.</t>
         </is>
       </c>
       <c r="M88" s="6" t="inlineStr">
@@ -15155,7 +15152,7 @@
       </c>
       <c r="T88" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U88" s="6" t="inlineStr">
@@ -15272,7 +15269,7 @@
       </c>
       <c r="L89" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q14.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q14.</t>
         </is>
       </c>
       <c r="M89" s="6" t="inlineStr">
@@ -15313,7 +15310,7 @@
       </c>
       <c r="T89" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U89" s="6" t="inlineStr">
@@ -15431,7 +15428,7 @@
       </c>
       <c r="L90" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q14.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q14.</t>
         </is>
       </c>
       <c r="M90" s="6" t="inlineStr">
@@ -15472,7 +15469,7 @@
       </c>
       <c r="T90" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U90" s="6" t="inlineStr">
@@ -15588,7 +15585,7 @@
       </c>
       <c r="L91" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q14.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q14.</t>
         </is>
       </c>
       <c r="M91" s="6" t="inlineStr">
@@ -15629,7 +15626,7 @@
       </c>
       <c r="T91" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U91" s="6" t="inlineStr">
@@ -15746,7 +15743,7 @@
       </c>
       <c r="L92" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q14.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q14.</t>
         </is>
       </c>
       <c r="M92" s="6" t="inlineStr">
@@ -15787,7 +15784,7 @@
       </c>
       <c r="T92" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U92" s="6" t="inlineStr">
@@ -15904,7 +15901,7 @@
       </c>
       <c r="L93" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q14.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q14.</t>
         </is>
       </c>
       <c r="M93" s="6" t="inlineStr">
@@ -15945,7 +15942,7 @@
       </c>
       <c r="T93" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U93" s="6" t="inlineStr">
@@ -16061,7 +16058,7 @@
       </c>
       <c r="L94" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q14.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q14.</t>
         </is>
       </c>
       <c r="M94" s="6" t="inlineStr">
@@ -16102,7 +16099,7 @@
       </c>
       <c r="T94" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U94" s="6" t="inlineStr">
@@ -16218,7 +16215,7 @@
       </c>
       <c r="L95" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q14.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q14.</t>
         </is>
       </c>
       <c r="M95" s="6" t="inlineStr">
@@ -16259,7 +16256,7 @@
       </c>
       <c r="T95" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U95" s="6" t="inlineStr">
@@ -19371,7 +19368,7 @@
       </c>
       <c r="L115" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q18.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q18.</t>
         </is>
       </c>
       <c r="M115" s="6" t="inlineStr">
@@ -19412,7 +19409,7 @@
       </c>
       <c r="T115" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U115" s="6" t="inlineStr">
@@ -19528,7 +19525,7 @@
       </c>
       <c r="L116" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q18.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q18.</t>
         </is>
       </c>
       <c r="M116" s="6" t="inlineStr">
@@ -19569,7 +19566,7 @@
       </c>
       <c r="T116" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U116" s="6" t="inlineStr">
@@ -19684,7 +19681,7 @@
       </c>
       <c r="L117" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q18.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q18.</t>
         </is>
       </c>
       <c r="M117" s="6" t="inlineStr">
@@ -19725,7 +19722,7 @@
       </c>
       <c r="T117" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U117" s="6" t="inlineStr">
@@ -19841,7 +19838,7 @@
       </c>
       <c r="L118" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q18.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q18.</t>
         </is>
       </c>
       <c r="M118" s="6" t="inlineStr">
@@ -19882,7 +19879,7 @@
       </c>
       <c r="T118" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U118" s="6" t="inlineStr">
@@ -19998,7 +19995,7 @@
       </c>
       <c r="L119" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q18.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q18.</t>
         </is>
       </c>
       <c r="M119" s="6" t="inlineStr">
@@ -20039,7 +20036,7 @@
       </c>
       <c r="T119" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U119" s="6" t="inlineStr">
@@ -20156,7 +20153,7 @@
       </c>
       <c r="L120" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q18.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q18.</t>
         </is>
       </c>
       <c r="M120" s="6" t="inlineStr">
@@ -20197,7 +20194,7 @@
       </c>
       <c r="T120" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U120" s="6" t="inlineStr">
@@ -20313,7 +20310,7 @@
       </c>
       <c r="L121" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q19.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q19.</t>
         </is>
       </c>
       <c r="M121" s="6" t="inlineStr">
@@ -20354,7 +20351,7 @@
       </c>
       <c r="T121" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U121" s="6" t="inlineStr">
@@ -20471,7 +20468,7 @@
       </c>
       <c r="L122" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q19.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q19.</t>
         </is>
       </c>
       <c r="M122" s="6" t="inlineStr">
@@ -20512,7 +20509,7 @@
       </c>
       <c r="T122" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U122" s="6" t="inlineStr">
@@ -20629,7 +20626,7 @@
       </c>
       <c r="L123" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q19.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q19.</t>
         </is>
       </c>
       <c r="M123" s="6" t="inlineStr">
@@ -20670,7 +20667,7 @@
       </c>
       <c r="T123" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U123" s="6" t="inlineStr">
@@ -20828,7 +20825,7 @@
       </c>
       <c r="T124" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U124" s="6" t="inlineStr">
@@ -20944,7 +20941,7 @@
       </c>
       <c r="L125" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q20.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q20.</t>
         </is>
       </c>
       <c r="M125" s="6" t="inlineStr">
@@ -20985,7 +20982,7 @@
       </c>
       <c r="T125" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U125" s="6" t="inlineStr">
@@ -21101,7 +21098,7 @@
       </c>
       <c r="L126" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q20.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q20.</t>
         </is>
       </c>
       <c r="M126" s="6" t="inlineStr">
@@ -21142,7 +21139,7 @@
       </c>
       <c r="T126" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U126" s="6" t="inlineStr">
@@ -21258,7 +21255,7 @@
       </c>
       <c r="L127" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q20.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q20.</t>
         </is>
       </c>
       <c r="M127" s="6" t="inlineStr">
@@ -21299,7 +21296,7 @@
       </c>
       <c r="T127" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U127" s="6" t="inlineStr">
@@ -21414,7 +21411,7 @@
       </c>
       <c r="L128" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q21.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q21.</t>
         </is>
       </c>
       <c r="M128" s="6" t="inlineStr">
@@ -21455,7 +21452,7 @@
       </c>
       <c r="T128" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U128" s="6" t="inlineStr">
@@ -21571,7 +21568,7 @@
       </c>
       <c r="L129" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q21.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q21.</t>
         </is>
       </c>
       <c r="M129" s="6" t="inlineStr">
@@ -21612,7 +21609,7 @@
       </c>
       <c r="T129" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U129" s="6" t="inlineStr">
@@ -21727,7 +21724,7 @@
       </c>
       <c r="L130" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q21.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q21.</t>
         </is>
       </c>
       <c r="M130" s="6" t="inlineStr">
@@ -21768,7 +21765,7 @@
       </c>
       <c r="T130" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U130" s="6" t="inlineStr">
@@ -21884,7 +21881,7 @@
       </c>
       <c r="L131" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q21.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q21.</t>
         </is>
       </c>
       <c r="M131" s="6" t="inlineStr">
@@ -21925,7 +21922,7 @@
       </c>
       <c r="T131" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U131" s="6" t="inlineStr">
@@ -22041,7 +22038,7 @@
       </c>
       <c r="L132" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q21.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q21.</t>
         </is>
       </c>
       <c r="M132" s="6" t="inlineStr">
@@ -22082,7 +22079,7 @@
       </c>
       <c r="T132" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U132" s="6" t="inlineStr">
@@ -22197,7 +22194,7 @@
       </c>
       <c r="L133" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q21.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q21.</t>
         </is>
       </c>
       <c r="M133" s="6" t="inlineStr">
@@ -22238,7 +22235,7 @@
       </c>
       <c r="T133" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U133" s="6" t="inlineStr">
@@ -22353,7 +22350,7 @@
       </c>
       <c r="L134" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q21.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q21.</t>
         </is>
       </c>
       <c r="M134" s="6" t="inlineStr">
@@ -22394,7 +22391,7 @@
       </c>
       <c r="T134" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U134" s="6" t="inlineStr">
@@ -22510,7 +22507,7 @@
       </c>
       <c r="L135" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as DT3.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as DT3.</t>
         </is>
       </c>
       <c r="M135" s="6" t="inlineStr">
@@ -22551,7 +22548,7 @@
       </c>
       <c r="T135" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U135" s="6" t="inlineStr">
@@ -22666,7 +22663,7 @@
       </c>
       <c r="L136" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D1.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as D1.</t>
         </is>
       </c>
       <c r="M136" s="6" t="inlineStr">
@@ -22707,7 +22704,7 @@
       </c>
       <c r="T136" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U136" s="6" t="inlineStr">
@@ -22823,7 +22820,7 @@
       </c>
       <c r="L137" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D1.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as D1.</t>
         </is>
       </c>
       <c r="M137" s="6" t="inlineStr">
@@ -22864,7 +22861,7 @@
       </c>
       <c r="T137" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U137" s="6" t="inlineStr">
@@ -23760,7 +23757,7 @@
       </c>
       <c r="L143" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D2.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as D2.</t>
         </is>
       </c>
       <c r="M143" s="6" t="inlineStr">
@@ -23801,7 +23798,7 @@
       </c>
       <c r="T143" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U143" s="6" t="inlineStr">
@@ -23917,7 +23914,7 @@
       </c>
       <c r="L144" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D2.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as D2.</t>
         </is>
       </c>
       <c r="M144" s="6" t="inlineStr">
@@ -23958,7 +23955,7 @@
       </c>
       <c r="T144" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U144" s="6" t="inlineStr">
@@ -24854,7 +24851,7 @@
       </c>
       <c r="L150" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D3.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as D3.</t>
         </is>
       </c>
       <c r="M150" s="6" t="inlineStr">
@@ -24895,7 +24892,7 @@
       </c>
       <c r="T150" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U150" s="6" t="inlineStr">
@@ -25011,7 +25008,7 @@
       </c>
       <c r="L151" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D3.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as D3.</t>
         </is>
       </c>
       <c r="M151" s="6" t="inlineStr">
@@ -25052,7 +25049,7 @@
       </c>
       <c r="T151" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U151" s="6" t="inlineStr">
@@ -25168,7 +25165,7 @@
       </c>
       <c r="L152" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D4.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as D4.</t>
         </is>
       </c>
       <c r="M152" s="6" t="inlineStr">
@@ -25209,7 +25206,7 @@
       </c>
       <c r="T152" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U152" s="6" t="inlineStr">
@@ -25325,7 +25322,7 @@
       </c>
       <c r="L153" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D4.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as D4.</t>
         </is>
       </c>
       <c r="M153" s="6" t="inlineStr">
@@ -25366,7 +25363,7 @@
       </c>
       <c r="T153" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U153" s="6" t="inlineStr">
@@ -25482,7 +25479,7 @@
       </c>
       <c r="L154" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q22.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q22.</t>
         </is>
       </c>
       <c r="M154" s="6" t="inlineStr">
@@ -25523,7 +25520,7 @@
       </c>
       <c r="T154" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U154" s="6" t="inlineStr">
@@ -25639,7 +25636,7 @@
       </c>
       <c r="L155" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q22.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q22.</t>
         </is>
       </c>
       <c r="M155" s="6" t="inlineStr">
@@ -25680,7 +25677,7 @@
       </c>
       <c r="T155" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U155" s="6" t="inlineStr">
@@ -25796,7 +25793,7 @@
       </c>
       <c r="L156" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q23.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q23.</t>
         </is>
       </c>
       <c r="M156" s="6" t="inlineStr">
@@ -25837,7 +25834,7 @@
       </c>
       <c r="T156" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U156" s="6" t="inlineStr">
@@ -25954,7 +25951,7 @@
       </c>
       <c r="L157" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q23.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q23.</t>
         </is>
       </c>
       <c r="M157" s="6" t="inlineStr">
@@ -25995,7 +25992,7 @@
       </c>
       <c r="T157" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U157" s="6" t="inlineStr">
@@ -26111,7 +26108,7 @@
       </c>
       <c r="L158" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q23.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q23.</t>
         </is>
       </c>
       <c r="M158" s="6" t="inlineStr">
@@ -26152,7 +26149,7 @@
       </c>
       <c r="T158" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U158" s="6" t="inlineStr">
@@ -26269,7 +26266,7 @@
       </c>
       <c r="L159" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q23.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q23.</t>
         </is>
       </c>
       <c r="M159" s="6" t="inlineStr">
@@ -26310,7 +26307,7 @@
       </c>
       <c r="T159" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U159" s="6" t="inlineStr">
@@ -26426,7 +26423,7 @@
       </c>
       <c r="L160" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q23.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q23.</t>
         </is>
       </c>
       <c r="M160" s="6" t="inlineStr">
@@ -26467,7 +26464,7 @@
       </c>
       <c r="T160" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U160" s="6" t="inlineStr">
@@ -26583,7 +26580,7 @@
       </c>
       <c r="L161" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q23.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q23.</t>
         </is>
       </c>
       <c r="M161" s="6" t="inlineStr">
@@ -26624,7 +26621,7 @@
       </c>
       <c r="T161" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U161" s="6" t="inlineStr">
@@ -26740,7 +26737,7 @@
       </c>
       <c r="L162" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q23.</t>
+          <t>Travel path P11 (Completing respondent — Q1=Open-source alternative; Q10=No; Q12=Not resolved) as far as Q23.</t>
         </is>
       </c>
       <c r="M162" s="6" t="inlineStr">
@@ -26781,7 +26778,7 @@
       </c>
       <c r="T162" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U162" s="6" t="inlineStr">
@@ -27012,7 +27009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -27175,7 +27172,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr"/>
@@ -27198,66 +27195,6 @@
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Shadowed branches - a finding, not a gap</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Q2 display rule</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>shadowed by R5</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Q2 carries a show-condition, and R5 jumps past it under the same circumstances. Whenever the show-condition would be false, the respondent has already been moved on, so the condition is never observed on its own. The two say the same thing. Worth confirming with the author that both are intended.</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>None for testing. Worth raising with the questionnaire author, since two rules say the same thing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Q3 display rule</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>shadowed by R5</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Q3 carries a show-condition, and R5 jumps past it under the same circumstances. Whenever the show-condition would be false, the respondent has already been moved on, so the condition is never observed on its own. The two say the same thing. Worth confirming with the author that both are intended.</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>None for testing. Worth raising with the questionnaire author, since two rules say the same thing.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:D4"/>
